--- a/results/DR_results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
+++ b/results/DR_results/01_pollution_assessment/HZD_Focus/tables/varpart_summary.xlsx
@@ -470,25 +470,25 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3161221134555727</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02790077677306035</v>
+        <v>0.08591857746673892</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3880141163418225</v>
+        <v>0.3147880571382554</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4159148931148828</v>
+        <v>0.2288694796715165</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0997927796593101</v>
+        <v>0.005038589754622791</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07189200288624975</v>
+        <v>0.08087998771211613</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6119858836581775</v>
+        <v>0.6852119428617446</v>
       </c>
     </row>
   </sheetData>
